--- a/resources/templates/Checklist_Positions/Template_SP2.xlsx
+++ b/resources/templates/Checklist_Positions/Template_SP2.xlsx
@@ -1029,7 +1029,7 @@
     <t>Recommended:</t>
   </si>
   <si>
-    <t>MA. CORAZON P. FEDEROSO</t>
+    <t>${encoder_name}</t>
   </si>
   <si>
     <t>RONALD KEVIN C. DEL ROSARIO</t>
@@ -1038,7 +1038,7 @@
     <t>VERNA C. CABAYA</t>
   </si>
   <si>
-    <t>Administrative Assistant III</t>
+    <t>${user_position}</t>
   </si>
   <si>
     <t>Administrative Officer IV-HR</t>
@@ -1047,7 +1047,7 @@
     <t>Administrative Officer V</t>
   </si>
   <si>
-    <t>Date: March 27, 2025</t>
+    <t>Date: ${date_of_signing}</t>
   </si>
   <si>
     <t>APC Form - (Revised 2018)</t>
@@ -1411,9 +1411,10 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <i/>
-      <sz val="9"/>
-      <color theme="1"/>
+      <sz val="8.5"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1427,10 +1428,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <i/>
-      <sz val="8.5"/>
-      <color rgb="FFFF0000"/>
+      <sz val="9"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
